--- a/invoice_extractor/templates/purchase_order_template.xlsx
+++ b/invoice_extractor/templates/purchase_order_template.xlsx
@@ -501,7 +501,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -750,6 +750,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1878,7 +1881,7 @@
     </row>
     <row r="26" ht="20.25" customHeight="1" s="54">
       <c r="B26" s="14" t="n"/>
-      <c r="C26" s="53" t="n"/>
+      <c r="C26" s="93" t="n"/>
       <c r="F26" s="52" t="n"/>
       <c r="G26" s="16" t="n"/>
       <c r="H26" s="55" t="n"/>
@@ -1887,7 +1890,7 @@
     </row>
     <row r="27" ht="21.75" customHeight="1" s="54">
       <c r="B27" s="18" t="n"/>
-      <c r="C27" s="53" t="n"/>
+      <c r="C27" s="93" t="n"/>
       <c r="F27" s="52" t="n"/>
       <c r="G27" s="15" t="n"/>
       <c r="H27" s="55" t="n"/>
@@ -1896,7 +1899,7 @@
     </row>
     <row r="28" ht="21" customHeight="1" s="54">
       <c r="B28" s="18" t="n"/>
-      <c r="C28" s="53" t="n"/>
+      <c r="C28" s="93" t="n"/>
       <c r="F28" s="52" t="n"/>
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="55" t="n"/>
@@ -1905,7 +1908,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1" s="54">
       <c r="B29" s="18" t="n"/>
-      <c r="C29" s="53" t="n"/>
+      <c r="C29" s="93" t="n"/>
       <c r="F29" s="52" t="n"/>
       <c r="G29" s="15" t="n"/>
       <c r="H29" s="55" t="n"/>
@@ -1914,7 +1917,7 @@
     </row>
     <row r="30" ht="18" customHeight="1" s="54">
       <c r="B30" s="9" t="n"/>
-      <c r="C30" s="53" t="n"/>
+      <c r="C30" s="93" t="n"/>
       <c r="F30" s="52" t="n"/>
       <c r="G30" s="19" t="n"/>
       <c r="H30" s="55" t="n"/>
@@ -1923,7 +1926,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" s="54">
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="53" t="n"/>
+      <c r="C31" s="93" t="n"/>
       <c r="F31" s="52" t="n"/>
       <c r="G31" s="19" t="n"/>
       <c r="H31" s="55" t="n"/>
@@ -1932,7 +1935,7 @@
     </row>
     <row r="32" ht="18" customHeight="1" s="54">
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="53" t="n"/>
+      <c r="C32" s="93" t="n"/>
       <c r="F32" s="52" t="n"/>
       <c r="G32" s="21" t="n"/>
       <c r="H32" s="55" t="n"/>
@@ -1941,7 +1944,7 @@
     </row>
     <row r="33" ht="18" customHeight="1" s="54">
       <c r="B33" s="9" t="n"/>
-      <c r="C33" s="53" t="n"/>
+      <c r="C33" s="93" t="n"/>
       <c r="F33" s="52" t="n"/>
       <c r="G33" s="21" t="n"/>
       <c r="H33" s="55" t="n"/>
@@ -1950,7 +1953,7 @@
     </row>
     <row r="34" ht="18" customHeight="1" s="54">
       <c r="B34" s="9" t="n"/>
-      <c r="C34" s="53" t="n"/>
+      <c r="C34" s="93" t="n"/>
       <c r="F34" s="52" t="n"/>
       <c r="G34" s="21" t="n"/>
       <c r="H34" s="55" t="n"/>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="35" ht="18" customHeight="1" s="54">
       <c r="B35" s="18" t="n"/>
-      <c r="C35" s="53" t="n"/>
+      <c r="C35" s="93" t="n"/>
       <c r="F35" s="52" t="n"/>
       <c r="G35" s="15" t="n"/>
       <c r="H35" s="55" t="n"/>
@@ -1968,7 +1971,7 @@
     </row>
     <row r="36" ht="18" customHeight="1" s="54">
       <c r="B36" s="18" t="n"/>
-      <c r="C36" s="53" t="n"/>
+      <c r="C36" s="93" t="n"/>
       <c r="F36" s="52" t="n"/>
       <c r="G36" s="15" t="n"/>
       <c r="H36" s="55" t="n"/>
@@ -1977,7 +1980,7 @@
     </row>
     <row r="37" ht="18" customHeight="1" s="54">
       <c r="B37" s="18" t="n"/>
-      <c r="C37" s="53" t="n"/>
+      <c r="C37" s="93" t="n"/>
       <c r="F37" s="52" t="n"/>
       <c r="G37" s="15" t="n"/>
       <c r="H37" s="55" t="n"/>
@@ -1986,7 +1989,7 @@
     </row>
     <row r="38" ht="18" customHeight="1" s="54">
       <c r="B38" s="18" t="n"/>
-      <c r="C38" s="53" t="n"/>
+      <c r="C38" s="93" t="n"/>
       <c r="F38" s="52" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="55" t="n"/>
@@ -1995,7 +1998,7 @@
     </row>
     <row r="39" ht="18" customHeight="1" s="54">
       <c r="B39" s="18" t="n"/>
-      <c r="C39" s="53" t="n"/>
+      <c r="C39" s="93" t="n"/>
       <c r="F39" s="52" t="n"/>
       <c r="G39" s="22" t="n"/>
       <c r="H39" s="55" t="n"/>
@@ -2004,7 +2007,7 @@
     </row>
     <row r="40" ht="18" customHeight="1" s="54">
       <c r="B40" s="18" t="n"/>
-      <c r="C40" s="53" t="n"/>
+      <c r="C40" s="93" t="n"/>
       <c r="F40" s="52" t="n"/>
       <c r="G40" s="15" t="n"/>
       <c r="H40" s="55" t="n"/>
@@ -2013,7 +2016,7 @@
     </row>
     <row r="41" ht="18" customHeight="1" s="54">
       <c r="B41" s="18" t="n"/>
-      <c r="C41" s="53" t="n"/>
+      <c r="C41" s="93" t="n"/>
       <c r="F41" s="52" t="n"/>
       <c r="G41" s="15" t="n"/>
       <c r="H41" s="55" t="n"/>
@@ -2022,7 +2025,7 @@
     </row>
     <row r="42" ht="18" customHeight="1" s="54">
       <c r="B42" s="18" t="n"/>
-      <c r="C42" s="53" t="n"/>
+      <c r="C42" s="93" t="n"/>
       <c r="F42" s="52" t="n"/>
       <c r="G42" s="15" t="n"/>
       <c r="H42" s="55" t="n"/>
@@ -2031,7 +2034,7 @@
     </row>
     <row r="43" ht="18" customHeight="1" s="54">
       <c r="B43" s="18" t="n"/>
-      <c r="C43" s="53" t="n"/>
+      <c r="C43" s="93" t="n"/>
       <c r="F43" s="52" t="n"/>
       <c r="G43" s="15" t="n"/>
       <c r="H43" s="51" t="n"/>
@@ -2040,7 +2043,7 @@
     </row>
     <row r="44" ht="18" customHeight="1" s="54">
       <c r="B44" s="18" t="n"/>
-      <c r="C44" s="53" t="n"/>
+      <c r="C44" s="93" t="n"/>
       <c r="F44" s="52" t="n"/>
       <c r="G44" s="15" t="n"/>
       <c r="H44" s="51" t="n"/>
@@ -2049,7 +2052,7 @@
     </row>
     <row r="45" ht="18" customHeight="1" s="54">
       <c r="B45" s="18" t="n"/>
-      <c r="C45" s="53" t="n"/>
+      <c r="C45" s="93" t="n"/>
       <c r="F45" s="52" t="n"/>
       <c r="G45" s="15" t="n"/>
       <c r="H45" s="51" t="n"/>
@@ -2058,7 +2061,7 @@
     </row>
     <row r="46" ht="18" customHeight="1" s="54">
       <c r="B46" s="18" t="n"/>
-      <c r="C46" s="53" t="n"/>
+      <c r="C46" s="93" t="n"/>
       <c r="F46" s="52" t="n"/>
       <c r="G46" s="15" t="n"/>
       <c r="H46" s="51" t="n"/>
@@ -2067,7 +2070,7 @@
     </row>
     <row r="47" ht="18" customHeight="1" s="54">
       <c r="B47" s="18" t="n"/>
-      <c r="C47" s="53" t="n"/>
+      <c r="C47" s="93" t="n"/>
       <c r="F47" s="52" t="n"/>
       <c r="G47" s="22" t="n"/>
       <c r="H47" s="51" t="n"/>
@@ -2076,7 +2079,7 @@
     </row>
     <row r="48" ht="18" customHeight="1" s="54">
       <c r="B48" s="18" t="n"/>
-      <c r="C48" s="53" t="n"/>
+      <c r="C48" s="93" t="n"/>
       <c r="F48" s="52" t="n"/>
       <c r="G48" s="22" t="n"/>
       <c r="H48" s="51" t="n"/>
@@ -2085,7 +2088,7 @@
     </row>
     <row r="49" ht="18" customHeight="1" s="54">
       <c r="B49" s="18" t="n"/>
-      <c r="C49" s="53" t="n"/>
+      <c r="C49" s="93" t="n"/>
       <c r="F49" s="52" t="n"/>
       <c r="G49" s="22" t="n"/>
       <c r="H49" s="51" t="n"/>
@@ -2094,7 +2097,7 @@
     </row>
     <row r="50" ht="18" customHeight="1" s="54">
       <c r="B50" s="18" t="n"/>
-      <c r="C50" s="53" t="n"/>
+      <c r="C50" s="93" t="n"/>
       <c r="F50" s="52" t="n"/>
       <c r="G50" s="22" t="n"/>
       <c r="H50" s="51" t="n"/>
@@ -2103,7 +2106,7 @@
     </row>
     <row r="51" ht="18" customHeight="1" s="54">
       <c r="B51" s="18" t="n"/>
-      <c r="C51" s="53" t="n"/>
+      <c r="C51" s="93" t="n"/>
       <c r="F51" s="52" t="n"/>
       <c r="G51" s="22" t="n"/>
       <c r="H51" s="51" t="n"/>
@@ -2112,7 +2115,7 @@
     </row>
     <row r="52" ht="18" customHeight="1" s="54">
       <c r="B52" s="18" t="n"/>
-      <c r="C52" s="53" t="n"/>
+      <c r="C52" s="93" t="n"/>
       <c r="F52" s="52" t="n"/>
       <c r="G52" s="16" t="n"/>
       <c r="H52" s="51" t="n"/>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="53" ht="18" customHeight="1" s="54">
       <c r="B53" s="18" t="n"/>
-      <c r="C53" s="53" t="n"/>
+      <c r="C53" s="93" t="n"/>
       <c r="F53" s="52" t="n"/>
       <c r="G53" s="23" t="n"/>
       <c r="H53" s="51" t="n"/>
@@ -2130,7 +2133,7 @@
     </row>
     <row r="54" ht="18" customHeight="1" s="54">
       <c r="B54" s="18" t="n"/>
-      <c r="C54" s="53" t="n"/>
+      <c r="C54" s="93" t="n"/>
       <c r="F54" s="52" t="n"/>
       <c r="G54" s="23" t="n"/>
       <c r="H54" s="73" t="n"/>
